--- a/astro-site/public/dl/plan-negocio-cocteleria-eventos/plantilla-proveedores-cocteleria-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-cocteleria-eventos/plantilla-proveedores-cocteleria-eventos.xlsx
@@ -19,7 +19,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. Captacion B2B" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. Hosply.pro" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'1. Licores y destilados'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'2. Mixers premium'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'3. Cristaleria'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'4. Hielo y refrigeracion'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'5. Equipamiento accesorio'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'6. Frutas y garnish'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'7. Consumibles eco'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'8. Servicios pro'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'9. Captacion B2B'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -166,6 +176,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -525,9 +545,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -550,10 +570,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Esta plantilla es el resultado de mas de 29 anos de experiencia en hosteleria, filtrada para identificar los proveedores REALES que necesitas para arrancar y operar una empresa de cocteleria de eventos en Espana. NO es una lista generica de Google: cada categoria incluye distribuidores oficiales, mayoristas validados y servicios complementarios necesarios para profesionalizar tu operacion desde el primer evento.
+          <t>Esta plantilla es el resultado de la experiencia de John Guerrero (en cocina desde los 17 años, consultor gastronómico desde 2010), filtrada para identificar los proveedores REALES que necesitas para arrancar y operar una empresa de cocteleria de eventos en Espana. NO es una lista generica de Google: cada categoria incluye distribuidores oficiales, mayoristas validados y servicios complementarios necesarios para profesionalizar tu operacion desde el primer evento.
 Los datos pueden variar con el tiempo (precios, condiciones, plazos). Verifica directamente con cada proveedor antes de cerrar acuerdos.</t>
         </is>
       </c>
@@ -561,6 +582,7 @@
     <row r="5"/>
     <row r="6"/>
     <row r="7"/>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
         <is>
@@ -688,6 +710,8 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="B22" s="4" t="inlineStr">
         <is>
@@ -791,13 +815,30 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/plan-negocio-cocteleria-eventos · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:D1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B4:D7"/>
+    <mergeCell ref="B1:D1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -805,7 +846,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -841,6 +882,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="9" t="inlineStr"/>
       <c r="B5" s="9" t="inlineStr">
@@ -1427,11 +1469,30 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A6:H18">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1439,9 +1500,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C21"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1456,6 +1517,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="8" t="inlineStr">
         <is>
@@ -1463,6 +1525,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -1474,6 +1537,7 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8"/>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
         <is>
@@ -1553,6 +1617,9 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
       <c r="B20" s="4" t="inlineStr">
         <is>
@@ -1570,9 +1637,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C8"/>
     <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B3:C3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId1"/>
@@ -1582,7 +1649,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId6"/>
   </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1590,7 +1666,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1626,6 +1702,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="9" t="inlineStr"/>
       <c r="B5" s="9" t="inlineStr">
@@ -2170,11 +2247,30 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A6:H17">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2182,7 +2278,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2218,6 +2314,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="9" t="inlineStr"/>
       <c r="B5" s="9" t="inlineStr">
@@ -2678,11 +2775,30 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A6:H15">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A6 A7 A8 A9 A10 A11 A12 A13 A14 A15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2690,7 +2806,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2726,6 +2842,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="9" t="inlineStr"/>
       <c r="B5" s="9" t="inlineStr">
@@ -3186,11 +3303,30 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A6:H15">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A6 A7 A8 A9 A10 A11 A12 A13 A14 A15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3198,7 +3334,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3234,6 +3370,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="9" t="inlineStr"/>
       <c r="B5" s="9" t="inlineStr">
@@ -3736,11 +3873,30 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A6:H16">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3748,7 +3904,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3784,6 +3940,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="9" t="inlineStr"/>
       <c r="B5" s="9" t="inlineStr">
@@ -4244,11 +4401,30 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A6:H15">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A6 A7 A8 A9 A10 A11 A12 A13 A14 A15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -4256,7 +4432,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4292,6 +4468,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="9" t="inlineStr"/>
       <c r="B5" s="9" t="inlineStr">
@@ -4752,11 +4929,30 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A6:H15">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A6 A7 A8 A9 A10 A11 A12 A13 A14 A15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -4764,7 +4960,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4800,6 +4996,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="9" t="inlineStr"/>
       <c r="B5" s="9" t="inlineStr">
@@ -5176,11 +5373,30 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A6:H13">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A6 A7 A8 A9 A10 A11 A12 A13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -5188,7 +5404,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5224,6 +5440,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="9" t="inlineStr"/>
       <c r="B5" s="9" t="inlineStr">
@@ -5768,10 +5985,29 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A6:H17">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>